--- a/artfynd/A 2008-2023 artfynd.xlsx
+++ b/artfynd/A 2008-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679526</v>
       </c>
       <c r="B2" t="n">
-        <v>78234</v>
+        <v>78236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>113679527</v>
       </c>
       <c r="B3" t="n">
-        <v>78199</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2008-2023 artfynd.xlsx
+++ b/artfynd/A 2008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679526</v>
+        <v>113679527</v>
       </c>
       <c r="B2" t="n">
-        <v>78236</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636957</v>
+        <v>636960</v>
       </c>
       <c r="R2" t="n">
-        <v>7054520</v>
+        <v>7054459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679527</v>
+        <v>113679526</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636960</v>
+        <v>636957</v>
       </c>
       <c r="R3" t="n">
-        <v>7054459</v>
+        <v>7054520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 2008-2023 artfynd.xlsx
+++ b/artfynd/A 2008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679527</v>
+        <v>113679526</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636960</v>
+        <v>636957</v>
       </c>
       <c r="R2" t="n">
-        <v>7054459</v>
+        <v>7054520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679526</v>
+        <v>113679527</v>
       </c>
       <c r="B3" t="n">
-        <v>78236</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636957</v>
+        <v>636960</v>
       </c>
       <c r="R3" t="n">
-        <v>7054520</v>
+        <v>7054459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 2008-2023 artfynd.xlsx
+++ b/artfynd/A 2008-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
